--- a/GameDesign/Excel/DropFishing.xlsx
+++ b/GameDesign/Excel/DropFishing.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -317,6 +317,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -682,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -690,7 +696,7 @@
     <col width="26" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
     <col width="10.5703125" customWidth="1" style="1" min="7" max="7"/>
     <col width="9.140625" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
@@ -1043,32 +1049,68 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="37" t="n"/>
-      <c r="C16" s="37" t="n"/>
-      <c r="D16" s="37" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="38" t="n"/>
+      <c r="B16" s="44" t="n">
+        <v>200109</v>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="44" t="n">
+        <v>100019</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv1</t>
+        </is>
+      </c>
       <c r="G16" s="37" t="n"/>
       <c r="H16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="37" t="n"/>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="37" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="38" t="n"/>
+      <c r="B17" s="44" t="n">
+        <v>200110</v>
+      </c>
+      <c r="C17" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="44" t="n">
+        <v>100020</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
+        <is>
+          <t>은 상자 Lv1</t>
+        </is>
+      </c>
+      <c r="G17" s="37" t="n"/>
       <c r="H17" s="37" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
+      <c r="B18" s="44" t="n">
+        <v>200111</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <v>100021</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="45" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv1</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="n"/>
       <c r="H18" s="37" t="n"/>
     </row>
     <row r="19">
@@ -1078,7 +1120,7 @@
       <c r="D19" s="37" t="n"/>
       <c r="E19" s="37" t="n"/>
       <c r="F19" s="38" t="n"/>
-      <c r="G19" s="38" t="n"/>
+      <c r="G19" s="37" t="n"/>
       <c r="H19" s="37" t="n"/>
     </row>
     <row r="20">
@@ -1118,7 +1160,7 @@
       <c r="D23" s="37" t="n"/>
       <c r="E23" s="37" t="n"/>
       <c r="F23" s="38" t="n"/>
-      <c r="G23" s="37" t="n"/>
+      <c r="G23" s="38" t="n"/>
       <c r="H23" s="37" t="n"/>
     </row>
     <row r="24">
@@ -1128,7 +1170,7 @@
       <c r="D24" s="37" t="n"/>
       <c r="E24" s="37" t="n"/>
       <c r="F24" s="38" t="n"/>
-      <c r="G24" s="37" t="n"/>
+      <c r="G24" s="38" t="n"/>
       <c r="H24" s="37" t="n"/>
     </row>
     <row r="25">
@@ -1138,7 +1180,7 @@
       <c r="D25" s="37" t="n"/>
       <c r="E25" s="37" t="n"/>
       <c r="F25" s="38" t="n"/>
-      <c r="G25" s="37" t="n"/>
+      <c r="G25" s="38" t="n"/>
       <c r="H25" s="37" t="n"/>
     </row>
     <row r="26">
@@ -3920,6 +3962,36 @@
       <c r="F303" s="38" t="n"/>
       <c r="G303" s="37" t="n"/>
       <c r="H303" s="37" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="37" t="n"/>
+      <c r="B304" s="37" t="n"/>
+      <c r="C304" s="37" t="n"/>
+      <c r="D304" s="37" t="n"/>
+      <c r="E304" s="37" t="n"/>
+      <c r="F304" s="38" t="n"/>
+      <c r="G304" s="37" t="n"/>
+      <c r="H304" s="37" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="37" t="n"/>
+      <c r="B305" s="37" t="n"/>
+      <c r="C305" s="37" t="n"/>
+      <c r="D305" s="37" t="n"/>
+      <c r="E305" s="37" t="n"/>
+      <c r="F305" s="38" t="n"/>
+      <c r="G305" s="37" t="n"/>
+      <c r="H305" s="37" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="37" t="n"/>
+      <c r="B306" s="37" t="n"/>
+      <c r="C306" s="37" t="n"/>
+      <c r="D306" s="37" t="n"/>
+      <c r="E306" s="37" t="n"/>
+      <c r="F306" s="38" t="n"/>
+      <c r="G306" s="37" t="n"/>
+      <c r="H306" s="37" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3932,7 +4004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -3940,7 +4012,7 @@
     <col width="26" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="22" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
     <col width="9.140625" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -4262,51 +4334,63 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="35" t="n">
-        <v>200207</v>
-      </c>
-      <c r="C16" s="35" t="n">
+      <c r="B16" s="44" t="n">
+        <v>200209</v>
+      </c>
+      <c r="C16" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="35" t="n">
-        <v>10001</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>붕어 — Lv1 하위 혼입</t>
+      <c r="D16" s="44" t="n">
+        <v>100022</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="35" t="n">
-        <v>200208</v>
-      </c>
-      <c r="C17" s="35" t="n">
+      <c r="B17" s="44" t="n">
+        <v>200210</v>
+      </c>
+      <c r="C17" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="35" t="n">
-        <v>10002</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>300</v>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>잉어 — Lv1 하위 혼입</t>
+      <c r="D17" s="44" t="n">
+        <v>100023</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
+        <is>
+          <t>은 상자 Lv2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="38" t="n"/>
+      <c r="B18" s="44" t="n">
+        <v>200211</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <v>100024</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="45" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -6603,6 +6687,14 @@
       <c r="D305" s="37" t="n"/>
       <c r="E305" s="37" t="n"/>
       <c r="F305" s="38" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="37" t="n"/>
+      <c r="B306" s="37" t="n"/>
+      <c r="C306" s="37" t="n"/>
+      <c r="D306" s="37" t="n"/>
+      <c r="E306" s="37" t="n"/>
+      <c r="F306" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6615,7 +6707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -6623,7 +6715,7 @@
     <col width="26" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="22" customWidth="1" style="1" min="6" max="6"/>
+    <col width="15" customWidth="1" style="1" min="6" max="6"/>
     <col width="9.140625" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -6945,51 +7037,63 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="35" t="n">
-        <v>200307</v>
-      </c>
-      <c r="C16" s="35" t="n">
+      <c r="B16" s="44" t="n">
+        <v>200309</v>
+      </c>
+      <c r="C16" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="35" t="n">
-        <v>10001</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>700</v>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>붕어 — Lv1 하위 혼입</t>
+      <c r="D16" s="44" t="n">
+        <v>100025</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="35" t="n">
-        <v>200308</v>
-      </c>
-      <c r="C17" s="35" t="n">
+      <c r="B17" s="44" t="n">
+        <v>200310</v>
+      </c>
+      <c r="C17" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="35" t="n">
-        <v>10002</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>200</v>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>잉어 — Lv1 하위 혼입</t>
+      <c r="D17" s="44" t="n">
+        <v>100026</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
+        <is>
+          <t>은 상자 Lv3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="38" t="n"/>
+      <c r="B18" s="44" t="n">
+        <v>200311</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <v>100027</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="45" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -9286,6 +9390,14 @@
       <c r="D305" s="37" t="n"/>
       <c r="E305" s="37" t="n"/>
       <c r="F305" s="38" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="37" t="n"/>
+      <c r="B306" s="37" t="n"/>
+      <c r="C306" s="37" t="n"/>
+      <c r="D306" s="37" t="n"/>
+      <c r="E306" s="37" t="n"/>
+      <c r="F306" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9298,7 +9410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -9306,7 +9418,7 @@
     <col width="26" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="22" customWidth="1" style="1" min="6" max="6"/>
+    <col width="15" customWidth="1" style="1" min="6" max="6"/>
     <col width="9.140625" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -9628,51 +9740,63 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="35" t="n">
-        <v>200407</v>
-      </c>
-      <c r="C16" s="35" t="n">
+      <c r="B16" s="44" t="n">
+        <v>200409</v>
+      </c>
+      <c r="C16" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="35" t="n">
-        <v>10001</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>400</v>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>붕어 — Lv1 하위 혼입</t>
+      <c r="D16" s="44" t="n">
+        <v>100028</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="35" t="n">
-        <v>200408</v>
-      </c>
-      <c r="C17" s="35" t="n">
+      <c r="B17" s="44" t="n">
+        <v>200410</v>
+      </c>
+      <c r="C17" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="35" t="n">
-        <v>10002</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>100</v>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>잉어 — Lv1 하위 혼입</t>
+      <c r="D17" s="44" t="n">
+        <v>100029</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
+        <is>
+          <t>은 상자 Lv4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="38" t="n"/>
+      <c r="B18" s="44" t="n">
+        <v>200411</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <v>100030</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="45" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv4</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -11969,6 +12093,14 @@
       <c r="D305" s="37" t="n"/>
       <c r="E305" s="37" t="n"/>
       <c r="F305" s="38" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="37" t="n"/>
+      <c r="B306" s="37" t="n"/>
+      <c r="C306" s="37" t="n"/>
+      <c r="D306" s="37" t="n"/>
+      <c r="E306" s="37" t="n"/>
+      <c r="F306" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11981,7 +12113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -11989,7 +12121,7 @@
     <col width="26" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="22" customWidth="1" style="1" min="6" max="6"/>
+    <col width="19" customWidth="1" style="1" min="6" max="6"/>
     <col width="9.140625" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -12311,51 +12443,63 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="35" t="n">
-        <v>200507</v>
-      </c>
-      <c r="C16" s="35" t="n">
+      <c r="B16" s="44" t="n">
+        <v>200509</v>
+      </c>
+      <c r="C16" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="35" t="n">
-        <v>10001</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>200</v>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t>붕어 — Lv1 하위 혼입</t>
+      <c r="D16" s="44" t="n">
+        <v>100031</v>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="35" t="n">
-        <v>200508</v>
-      </c>
-      <c r="C17" s="35" t="n">
+      <c r="B17" s="44" t="n">
+        <v>200510</v>
+      </c>
+      <c r="C17" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="35" t="n">
-        <v>10002</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>50</v>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t>잉어 — Lv1 하위 혼입</t>
+      <c r="D17" s="44" t="n">
+        <v>100032</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
+        <is>
+          <t>은 상자 Lv5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="38" t="n"/>
+      <c r="B18" s="44" t="n">
+        <v>200511</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <v>100033</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="45" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv5</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -14653,6 +14797,14 @@
       <c r="E305" s="37" t="n"/>
       <c r="F305" s="38" t="n"/>
     </row>
+    <row r="306">
+      <c r="A306" s="37" t="n"/>
+      <c r="B306" s="37" t="n"/>
+      <c r="C306" s="37" t="n"/>
+      <c r="D306" s="37" t="n"/>
+      <c r="E306" s="37" t="n"/>
+      <c r="F306" s="38" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameDesign/Excel/DropFishing.xlsx
+++ b/GameDesign/Excel/DropFishing.xlsx
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -696,7 +696,7 @@
     <col width="26" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="13" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
     <col width="10.5703125" customWidth="1" style="1" min="7" max="7"/>
     <col width="9.140625" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
@@ -1049,68 +1049,32 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>200109</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>100019</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv1</t>
-        </is>
-      </c>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="38" t="n"/>
       <c r="G16" s="37" t="n"/>
       <c r="H16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>200110</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>100020</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>은 상자 Lv1</t>
-        </is>
-      </c>
-      <c r="G17" s="37" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="38" t="n"/>
       <c r="H17" s="37" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="44" t="n">
-        <v>200111</v>
-      </c>
-      <c r="C18" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="44" t="n">
-        <v>100021</v>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="45" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv1</t>
-        </is>
-      </c>
-      <c r="G18" s="37" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="38" t="n"/>
       <c r="H18" s="37" t="n"/>
     </row>
     <row r="19">
@@ -1120,7 +1084,7 @@
       <c r="D19" s="37" t="n"/>
       <c r="E19" s="37" t="n"/>
       <c r="F19" s="38" t="n"/>
-      <c r="G19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
       <c r="H19" s="37" t="n"/>
     </row>
     <row r="20">
@@ -1160,7 +1124,7 @@
       <c r="D23" s="37" t="n"/>
       <c r="E23" s="37" t="n"/>
       <c r="F23" s="38" t="n"/>
-      <c r="G23" s="38" t="n"/>
+      <c r="G23" s="37" t="n"/>
       <c r="H23" s="37" t="n"/>
     </row>
     <row r="24">
@@ -1170,7 +1134,7 @@
       <c r="D24" s="37" t="n"/>
       <c r="E24" s="37" t="n"/>
       <c r="F24" s="38" t="n"/>
-      <c r="G24" s="38" t="n"/>
+      <c r="G24" s="37" t="n"/>
       <c r="H24" s="37" t="n"/>
     </row>
     <row r="25">
@@ -1180,7 +1144,7 @@
       <c r="D25" s="37" t="n"/>
       <c r="E25" s="37" t="n"/>
       <c r="F25" s="38" t="n"/>
-      <c r="G25" s="38" t="n"/>
+      <c r="G25" s="37" t="n"/>
       <c r="H25" s="37" t="n"/>
     </row>
     <row r="26">
@@ -3962,36 +3926,6 @@
       <c r="F303" s="38" t="n"/>
       <c r="G303" s="37" t="n"/>
       <c r="H303" s="37" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="37" t="n"/>
-      <c r="B304" s="37" t="n"/>
-      <c r="C304" s="37" t="n"/>
-      <c r="D304" s="37" t="n"/>
-      <c r="E304" s="37" t="n"/>
-      <c r="F304" s="38" t="n"/>
-      <c r="G304" s="37" t="n"/>
-      <c r="H304" s="37" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="37" t="n"/>
-      <c r="B305" s="37" t="n"/>
-      <c r="C305" s="37" t="n"/>
-      <c r="D305" s="37" t="n"/>
-      <c r="E305" s="37" t="n"/>
-      <c r="F305" s="38" t="n"/>
-      <c r="G305" s="37" t="n"/>
-      <c r="H305" s="37" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="37" t="n"/>
-      <c r="B306" s="37" t="n"/>
-      <c r="C306" s="37" t="n"/>
-      <c r="D306" s="37" t="n"/>
-      <c r="E306" s="37" t="n"/>
-      <c r="F306" s="38" t="n"/>
-      <c r="G306" s="37" t="n"/>
-      <c r="H306" s="37" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4004,7 +3938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -4334,63 +4268,27 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>200209</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>100022</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv2</t>
-        </is>
-      </c>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="38" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>200210</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>100023</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>은 상자 Lv2</t>
-        </is>
-      </c>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="44" t="n">
-        <v>200211</v>
-      </c>
-      <c r="C18" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="44" t="n">
-        <v>100024</v>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="45" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv2</t>
-        </is>
-      </c>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -6671,30 +6569,6 @@
       <c r="D303" s="37" t="n"/>
       <c r="E303" s="37" t="n"/>
       <c r="F303" s="38" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="37" t="n"/>
-      <c r="B304" s="37" t="n"/>
-      <c r="C304" s="37" t="n"/>
-      <c r="D304" s="37" t="n"/>
-      <c r="E304" s="37" t="n"/>
-      <c r="F304" s="38" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="37" t="n"/>
-      <c r="B305" s="37" t="n"/>
-      <c r="C305" s="37" t="n"/>
-      <c r="D305" s="37" t="n"/>
-      <c r="E305" s="37" t="n"/>
-      <c r="F305" s="38" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="37" t="n"/>
-      <c r="B306" s="37" t="n"/>
-      <c r="C306" s="37" t="n"/>
-      <c r="D306" s="37" t="n"/>
-      <c r="E306" s="37" t="n"/>
-      <c r="F306" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +6581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -6715,7 +6589,7 @@
     <col width="26" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="15" customWidth="1" style="1" min="6" max="6"/>
+    <col width="13" customWidth="1" style="1" min="6" max="6"/>
     <col width="9.140625" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -7037,63 +6911,27 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>200309</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>100025</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv3</t>
-        </is>
-      </c>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="38" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>200310</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>100026</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>은 상자 Lv3</t>
-        </is>
-      </c>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="44" t="n">
-        <v>200311</v>
-      </c>
-      <c r="C18" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="44" t="n">
-        <v>100027</v>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="45" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv3</t>
-        </is>
-      </c>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -9374,30 +9212,6 @@
       <c r="D303" s="37" t="n"/>
       <c r="E303" s="37" t="n"/>
       <c r="F303" s="38" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="37" t="n"/>
-      <c r="B304" s="37" t="n"/>
-      <c r="C304" s="37" t="n"/>
-      <c r="D304" s="37" t="n"/>
-      <c r="E304" s="37" t="n"/>
-      <c r="F304" s="38" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="37" t="n"/>
-      <c r="B305" s="37" t="n"/>
-      <c r="C305" s="37" t="n"/>
-      <c r="D305" s="37" t="n"/>
-      <c r="E305" s="37" t="n"/>
-      <c r="F305" s="38" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="37" t="n"/>
-      <c r="B306" s="37" t="n"/>
-      <c r="C306" s="37" t="n"/>
-      <c r="D306" s="37" t="n"/>
-      <c r="E306" s="37" t="n"/>
-      <c r="F306" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9410,7 +9224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -9418,7 +9232,7 @@
     <col width="26" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="15" customWidth="1" style="1" min="6" max="6"/>
+    <col width="13" customWidth="1" style="1" min="6" max="6"/>
     <col width="9.140625" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -9740,63 +9554,27 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>200409</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>100028</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv4</t>
-        </is>
-      </c>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="38" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>200410</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>100029</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>은 상자 Lv4</t>
-        </is>
-      </c>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="44" t="n">
-        <v>200411</v>
-      </c>
-      <c r="C18" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="44" t="n">
-        <v>100030</v>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="45" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv4</t>
-        </is>
-      </c>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -12077,30 +11855,6 @@
       <c r="D303" s="37" t="n"/>
       <c r="E303" s="37" t="n"/>
       <c r="F303" s="38" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="37" t="n"/>
-      <c r="B304" s="37" t="n"/>
-      <c r="C304" s="37" t="n"/>
-      <c r="D304" s="37" t="n"/>
-      <c r="E304" s="37" t="n"/>
-      <c r="F304" s="38" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="37" t="n"/>
-      <c r="B305" s="37" t="n"/>
-      <c r="C305" s="37" t="n"/>
-      <c r="D305" s="37" t="n"/>
-      <c r="E305" s="37" t="n"/>
-      <c r="F305" s="38" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="37" t="n"/>
-      <c r="B306" s="37" t="n"/>
-      <c r="C306" s="37" t="n"/>
-      <c r="D306" s="37" t="n"/>
-      <c r="E306" s="37" t="n"/>
-      <c r="F306" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12113,7 +11867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -12443,63 +12197,27 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>200509</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>100031</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv5</t>
-        </is>
-      </c>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="38" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>200510</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>100032</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>은 상자 Lv5</t>
-        </is>
-      </c>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="n"/>
-      <c r="B18" s="44" t="n">
-        <v>200511</v>
-      </c>
-      <c r="C18" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="44" t="n">
-        <v>100033</v>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="45" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv5</t>
-        </is>
-      </c>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="37" t="n"/>
@@ -14781,30 +14499,6 @@
       <c r="E303" s="37" t="n"/>
       <c r="F303" s="38" t="n"/>
     </row>
-    <row r="304">
-      <c r="A304" s="37" t="n"/>
-      <c r="B304" s="37" t="n"/>
-      <c r="C304" s="37" t="n"/>
-      <c r="D304" s="37" t="n"/>
-      <c r="E304" s="37" t="n"/>
-      <c r="F304" s="38" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="37" t="n"/>
-      <c r="B305" s="37" t="n"/>
-      <c r="C305" s="37" t="n"/>
-      <c r="D305" s="37" t="n"/>
-      <c r="E305" s="37" t="n"/>
-      <c r="F305" s="38" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="37" t="n"/>
-      <c r="B306" s="37" t="n"/>
-      <c r="C306" s="37" t="n"/>
-      <c r="D306" s="37" t="n"/>
-      <c r="E306" s="37" t="n"/>
-      <c r="F306" s="38" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
